--- a/src/main/resources/SheetJSFileUploadDateTime.xlsx
+++ b/src/main/resources/SheetJSFileUploadDateTime.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22325"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23530"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workpace-gov-grants-framework-automation\govgrants-framework-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ASHWINI\AUTOMATION\govgrants-framework-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B42867DD-E814-42DA-8D4D-FAC8378DEDCA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB440DF4-8AA8-4842-8096-8BD466FD996B}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10395" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="35">
   <si>
     <t>ID</t>
   </si>
@@ -123,6 +123,9 @@
   </si>
   <si>
     <t>2021-07-03T02:07:00</t>
+  </si>
+  <si>
+    <t>09/16/2025</t>
   </si>
 </sst>
 </file>
@@ -500,22 +503,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K2"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.8125" customWidth="1"/>
-    <col min="2" max="2" width="17.8125" customWidth="1"/>
-    <col min="3" max="3" width="38.3125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.8125" customWidth="1"/>
-    <col min="5" max="5" width="28.8125" customWidth="1"/>
-    <col min="6" max="6" width="30.8125" customWidth="1"/>
-    <col min="7" max="7" width="27.8125" customWidth="1"/>
-    <col min="8" max="8" width="29.8125" customWidth="1"/>
-    <col min="9" max="9" width="24.8125" customWidth="1"/>
-    <col min="10" max="10" width="31.8125" customWidth="1"/>
-    <col min="11" max="11" width="26.8125" customWidth="1"/>
+    <col min="1" max="1" width="19.875" customWidth="1"/>
+    <col min="2" max="2" width="17.875" customWidth="1"/>
+    <col min="3" max="3" width="38.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.875" customWidth="1"/>
+    <col min="5" max="5" width="28.875" customWidth="1"/>
+    <col min="6" max="6" width="30.875" customWidth="1"/>
+    <col min="7" max="7" width="27.875" customWidth="1"/>
+    <col min="8" max="8" width="29.875" customWidth="1"/>
+    <col min="9" max="9" width="24.875" customWidth="1"/>
+    <col min="10" max="10" width="31.875" customWidth="1"/>
+    <col min="11" max="11" width="26.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -550,12 +553,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
         <v>31</v>
       </c>
       <c r="D2" t="s">
         <v>32</v>
+      </c>
+      <c r="G2" t="s">
+        <v>34</v>
       </c>
       <c r="H2" t="s">
         <v>33</v>
@@ -573,22 +579,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K5"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.8125" customWidth="1"/>
-    <col min="2" max="2" width="17.8125" customWidth="1"/>
-    <col min="3" max="3" width="29.8125" customWidth="1"/>
-    <col min="4" max="4" width="25.8125" customWidth="1"/>
-    <col min="5" max="5" width="28.8125" customWidth="1"/>
-    <col min="6" max="6" width="30.8125" customWidth="1"/>
-    <col min="7" max="7" width="27.8125" customWidth="1"/>
-    <col min="8" max="8" width="29.8125" customWidth="1"/>
-    <col min="9" max="9" width="24.8125" customWidth="1"/>
-    <col min="10" max="10" width="31.8125" customWidth="1"/>
-    <col min="11" max="11" width="26.8125" customWidth="1"/>
+    <col min="1" max="1" width="19.875" customWidth="1"/>
+    <col min="2" max="2" width="17.875" customWidth="1"/>
+    <col min="3" max="3" width="29.875" customWidth="1"/>
+    <col min="4" max="4" width="25.875" customWidth="1"/>
+    <col min="5" max="5" width="28.875" customWidth="1"/>
+    <col min="6" max="6" width="30.875" customWidth="1"/>
+    <col min="7" max="7" width="27.875" customWidth="1"/>
+    <col min="8" max="8" width="29.875" customWidth="1"/>
+    <col min="9" max="9" width="24.875" customWidth="1"/>
+    <col min="10" max="10" width="31.875" customWidth="1"/>
+    <col min="11" max="11" width="26.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -623,7 +629,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -658,7 +664,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>28</v>
       </c>
@@ -693,7 +699,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>29</v>
       </c>
@@ -728,7 +734,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>0</v>
       </c>
